--- a/AAII_Financials/Quarterly/SRGHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SRGHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>SRGHY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,59 +656,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -736,8 +743,14 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -765,8 +778,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -794,8 +813,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,8 +832,10 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -836,8 +863,14 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,8 +898,14 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -894,8 +933,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -923,8 +968,14 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,8 +984,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -962,8 +1015,14 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -991,8 +1050,14 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1069,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1033,8 +1100,14 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1062,8 +1135,14 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1091,8 +1170,14 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1120,8 +1205,14 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1149,8 +1240,14 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,8 +1275,14 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1207,8 +1310,14 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1236,8 +1345,14 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1380,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,8 +1415,14 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1450,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,8 +1485,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1381,8 +1520,14 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1410,8 +1555,14 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,8 +1590,14 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1468,42 +1625,54 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1684,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,269 +1699,325 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>599700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>654800</v>
+      </c>
+      <c r="F41" s="3">
         <v>642700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>621000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>521500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>505600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>666200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>708300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>559900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>528300</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F42" s="3">
         <v>70600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>68200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>84900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>82300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>42700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>45400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>66900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>63200</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>464800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>507600</v>
+      </c>
+      <c r="F43" s="3">
         <v>422600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>408300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>484600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>469800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>397300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>422500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>415100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>391700</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1751400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1912300</v>
+      </c>
+      <c r="F44" s="3">
         <v>1553900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1501500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1600300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1551500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1332100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1416300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1492100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>303100</v>
+      </c>
+      <c r="F45" s="3">
         <v>52400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>50600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>57100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>55400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>73700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>78400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>78000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3109800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3395500</v>
+      </c>
+      <c r="F46" s="3">
         <v>2742200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2649800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2778400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2693700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2546500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2707500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2635200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2486700</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>166400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>181700</v>
+      </c>
+      <c r="F47" s="3">
         <v>146500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>141500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>135400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>131200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>167600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>178200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>192500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>181600</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2913800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3181500</v>
+      </c>
+      <c r="F48" s="3">
         <v>2746700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2654100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2516300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2439600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2303200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2448800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2405200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2269700</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>304900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>332900</v>
+      </c>
+      <c r="F49" s="3">
         <v>257200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>248500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>242700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>235300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>224300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>238500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>225300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +2045,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,23 +2080,29 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F52" s="3">
         <v>33800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>32700</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
@@ -1876,8 +2115,14 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,37 +2150,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6746600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7366400</v>
+      </c>
+      <c r="F54" s="3">
         <v>6153200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5945800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5902900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5722900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5439200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5783100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5706100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5384500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2204,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,182 +2219,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2065900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2255700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1778000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1718100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1804900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1749900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1332900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1417200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1693700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1598200</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>518400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>566100</v>
+      </c>
+      <c r="F58" s="3">
         <v>376600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>363900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>319300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>309600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>546900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>581500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>292100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>203600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>222300</v>
+      </c>
+      <c r="F59" s="3">
         <v>112700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>108900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>96500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>93500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>98200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>104400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2798000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3055000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2275400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2198700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2229900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2161900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1987800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2113500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2086100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1968500</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2442500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2666900</v>
+      </c>
+      <c r="F61" s="3">
         <v>2327600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2249100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2185600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2118900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2030800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2159300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2070600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1953900</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
         <v>14500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>14000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>12000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>21200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2460,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2495,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,37 +2530,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5263400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5746900</v>
+      </c>
+      <c r="F66" s="3">
         <v>4634500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4478300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4444200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4308600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4044100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4299800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4178400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3942900</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2584,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2615,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,8 +2650,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2350,8 +2685,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,37 +2720,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1741300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1901200</v>
+      </c>
+      <c r="F72" s="3">
         <v>1707600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1650000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1624700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1575200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1520300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1616500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1601700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1511400</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +2790,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +2825,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,37 +2860,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1488100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1624700</v>
+      </c>
+      <c r="F76" s="3">
         <v>1522400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1471100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1452400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1408100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1387300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1475000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1519100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1433500</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,42 +2930,54 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2616,8 +3005,14 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,37 +3024,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>95500</v>
+      </c>
+      <c r="F83" s="3">
         <v>86300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>91800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>92200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>87000</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>84900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +3090,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +3125,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +3160,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +3195,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,37 +3230,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>184900</v>
+      </c>
+      <c r="F89" s="3">
         <v>221500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>214100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>259600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>251700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>101600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>108000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>275700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,37 +3284,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-111900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-122200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-110500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-106800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-101900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-98800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-89600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-95300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-98800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-93200</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3350,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,37 +3385,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-114700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-89800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-86800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-95600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-92700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-72900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-77600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-102400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,37 +3439,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>71200</v>
+      </c>
+      <c r="F96" s="3">
         <v>40300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>39000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>62100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>60200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>36100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>38400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>59100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>55800</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3505,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +3540,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,91 +3575,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-157500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-108000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-104400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-104200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-101000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-82500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-87700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-91700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-86500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-2600</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>11200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-91500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="F102" s="3">
         <v>21500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>20800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>47800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>46400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-62400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-66300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>78900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>74500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SRGHY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SRGHY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>SRGHY</t>
   </si>
@@ -656,74 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45928</v>
+      </c>
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +770,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,8 +817,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -845,8 +864,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +887,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,8 +930,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +977,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -985,8 +1024,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,8 +1071,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,8 +1091,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1081,8 +1134,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1122,8 +1181,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,8 +1204,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1180,8 +1247,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1221,8 +1294,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1262,8 +1341,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1303,8 +1388,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1344,8 +1435,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,8 +1482,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1426,8 +1529,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1467,8 +1576,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1623,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1670,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1717,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,8 +1764,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1672,8 +1811,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1713,8 +1858,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,8 +1905,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1795,54 +1952,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45928</v>
+      </c>
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +2027,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,377 +2046,433 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>903800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>869000</v>
+      </c>
+      <c r="F41" s="3">
         <v>558100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>540900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>599700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>654800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>642700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>621000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>521500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>505600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>666200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>708300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>559900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>528300</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F42" s="3">
         <v>7000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>6800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>16300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>17700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>70600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>68200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>84900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>82300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>42700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>45400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>66900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>63200</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>474000</v>
+      </c>
+      <c r="F43" s="3">
         <v>418300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>405400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>464800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>507600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>422600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>408300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>484600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>469800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>397300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>422500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>415100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>391700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2022600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1944700</v>
+      </c>
+      <c r="F44" s="3">
         <v>1669200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1617900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1751400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1912300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1553900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1501500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1600300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1551500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1332100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1416300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1492100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1408000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>251100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>241500</v>
+      </c>
+      <c r="F45" s="3">
         <v>313600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>303900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>277600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>303100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>52400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>50600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>57100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>55400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>73700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>78400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>78000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>73600</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3680400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3538800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2966500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2875200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3109800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3395500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2742200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2649800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2778400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2693700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2546500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2707500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2635200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2486700</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>171100</v>
+      </c>
+      <c r="F47" s="3">
         <v>174200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>168800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>166400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>181700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>146500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>141500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>135400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>131200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>167600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>178200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>192500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>181600</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3747200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3603000</v>
+      </c>
+      <c r="F48" s="3">
         <v>3289700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3188400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2913800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3181500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2746700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2654100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2516300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2439600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2303200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2448800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2405200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2269700</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>341300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>328200</v>
+      </c>
+      <c r="F49" s="3">
         <v>319800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>310000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>304900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>332900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>257200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>248500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>242700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>235300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>224300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>238500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>225300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>212600</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2512,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,35 +2559,41 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F52" s="3">
         <v>7200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>7000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>28900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>31600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>33800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>32700</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2367,8 +2606,14 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,49 +2653,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8210500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7894600</v>
+      </c>
+      <c r="F54" s="3">
         <v>7011000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6795200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6746600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>7366400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6153200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5945800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5902900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5722900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5439200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5783100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>5706100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5384500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2723,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,254 +2742,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2634100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2532700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1912600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1853700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2065900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2255700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1778000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1718100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1804900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1749900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1332900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1417200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1693700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1598200</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>269300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>259000</v>
+      </c>
+      <c r="F58" s="3">
         <v>351000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>340200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>518400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>566100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>376600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>363900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>319300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>309600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>546900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>581500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>292100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>275600</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>267400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>257100</v>
+      </c>
+      <c r="F59" s="3">
         <v>228700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>221700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>203600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>222300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>112700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>108900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>96500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>93500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>98200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>104400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>100300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>94600</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3177100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3054900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2499300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2422400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2798000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3055000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2275400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2198700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2229900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2161900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1987800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2113500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2086100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1968500</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3156100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3034600</v>
+      </c>
+      <c r="F61" s="3">
         <v>2784300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2698600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2442500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2666900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2327600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2249100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2185600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2118900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2030800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2159300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2070600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1953900</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F62" s="3">
         <v>17700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>17100</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>14500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>14000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>12000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>12800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>21200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +3067,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +3114,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,49 +3161,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6374700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6129400</v>
+      </c>
+      <c r="F66" s="3">
         <v>5321000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5157300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5263400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5746900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4634500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4478300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4444200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4308600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4044100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4299800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4178400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3942900</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3231,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3274,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3321,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3368,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,49 +3415,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2145100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2062600</v>
+      </c>
+      <c r="F72" s="3">
         <v>1951600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1891500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1741300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1901200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1707600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1650000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1624700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1575200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1520300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1616500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1601700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1511400</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3509,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3556,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,49 +3603,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1840300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1769500</v>
+      </c>
+      <c r="F76" s="3">
         <v>1694300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1642100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1488100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1624700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1522400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1471100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1452400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1408100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1387300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1475000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1519100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1433500</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,54 +3697,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45928</v>
+      </c>
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3407,8 +3796,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,49 +3819,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>123700</v>
+      </c>
+      <c r="F83" s="3">
         <v>100300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>96900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>98500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>95500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>86300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>91800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>92200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>87000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>84900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3909,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3956,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +4003,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +4050,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,49 +4097,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>481500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>463000</v>
+      </c>
+      <c r="F89" s="3">
         <v>242800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>235300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>169400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>184900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>221500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>214100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>259600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>251700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>101600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>108000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>275700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>260200</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,49 +4167,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-117800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-113300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-107700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-104400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-111900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-122200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-110500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-106800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-101900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-98800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-89600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-95300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-98800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-93200</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4257,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,49 +4304,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-106700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-102600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-96800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-93800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-105000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-114700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-89800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-86800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-95600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-92700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-72900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-77600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-102400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,49 +4374,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>77700</v>
+      </c>
+      <c r="F96" s="3">
         <v>43600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>42300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>65200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>71200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>40300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>39000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>62100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>60200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>36100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>38400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>59100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>55800</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4464,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4511,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,127 +4558,151 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-195400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-187900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-67600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-65600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-157500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-172000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-108000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-104400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-104200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-101000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-82500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-87700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-91700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-86500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-11900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-11500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-8500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3">
         <v>11200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>173100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>166400</v>
+      </c>
+      <c r="F102" s="3">
         <v>75700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>73400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-91500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-100000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>21500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>20800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>47800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>46400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-62400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-66300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>78900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>74500</v>
       </c>
     </row>
